--- a/SurveyQuestions/outputs/MECAMH_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/MECAMH_question_score_reordered.xlsx
@@ -21,13 +21,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -60,7 +63,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -68,23 +71,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>

--- a/SurveyQuestions/outputs/MECAMH_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/MECAMH_question_score_reordered.xlsx
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -63,7 +60,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -71,31 +68,23 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>

--- a/SurveyQuestions/outputs/MECAMH_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/MECAMH_question_score_reordered.xlsx
@@ -770,7 +770,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Climate Change Worry (Ojala 2012)</t>
+          <t xml:space="preserve">  ↳ Climate Change Worry</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -781,7 +781,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Coping Responses (Ojala 2012)</t>
+          <t xml:space="preserve">  ↳ Coping Responses</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -803,7 +803,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ [State] Anxiety (modelled on the STAI)</t>
+          <t xml:space="preserve">  ↳ Anxiety</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -814,7 +814,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Anticipatory Traumatic Reaction – Feelings Sub-Scale (Hopwood et al. 2017)</t>
+          <t xml:space="preserve">  ↳ Anticipatory Traumatic Reaction</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Climate Change Worry (Ojala 2012)</t>
+          <t>Climate Change Worry</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Coping Responses (Ojala 2012)</t>
+          <t>Coping Responses</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr"/>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>[State] Anxiety (modelled on the STAI)</t>
+          <t>Anxiety</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Anticipatory Traumatic Reaction – Feelings Sub-Scale (Hopwood et al. 2017)</t>
+          <t>Anticipatory Traumatic Reaction</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr"/>
